--- a/daily_matches/job_matches_2026-09-13.xlsx
+++ b/daily_matches/job_matches_2026-09-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,217 +468,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer III - Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FAISS, Pinecone, TensorFlow, PyTorch, S3, MLflow, Docker</t>
+          <t>Data Scientist, RAG, Copilot, S3, Glue, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c474e6ef0d9a03</t>
+          <t>https://www.indeed.com/viewjob?jk=abb83d271754206d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jr. AI Developer - Korean Bilingual MUST</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, RAG, S3, Glue, CI/CD, Jenkins, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c1154e8a781d96b</t>
+          <t>https://www.indeed.com/viewjob?jk=099249332f619f68</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, TensorFlow</t>
+          <t>Data Scientist, Redshift, BigQuery, Data Lake, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer, Foundations</t>
+          <t>Personalization Product Senior Data Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec18260f61a8b7c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Azure ML</t>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa073332dbb902f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1f026d04afe119e3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Azure ML</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1dd3a9c03fc083</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bc69f7ee34b797</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,690 +688,165 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
+          <t>RAG, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5ac038b52e4c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8a2058924a345e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Workflow Optimization Engineer</t>
+          <t>Software Engineer III - Java/AWS/Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, FAISS, TensorFlow, AWS SageMaker, Hadoop, Power BI, Python</t>
+          <t>RAG, S3, CI/CD, Terraform, Databricks, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4fe86d26fe3ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=31d293ae32e73a40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, Prompt Engineering, Docker, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
+          <t>https://www.indeed.com/viewjob?jk=6133400dd8a88a97</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Co-op: Engineering, Data Science (Spring 2027)</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Volvo Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Power BI, Matplotlib, Python</t>
+          <t>RAG, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb3f849b7283fda</t>
+          <t>https://www.indeed.com/viewjob?jk=84607e3a06c12fdd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote Opportunity!</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, MLflow, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, Databricks, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4badb7c2f63bb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Applied AI SRE III - PxE GPS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd2be904c4c0519c</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed98dbffc18b3499</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Web Analytics</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LatentView Analytics</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f27e4e0e461509</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Senior</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, S3, AKS, CI/CD, Git, Tableau, Power BI, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82b117a450c05355</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Data Platform Engineer AWS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Redshift, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44e49801926d6f34</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2d3fa65c104128</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer III- AI/ML Engineering, GPU ML Serving</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Cassandra, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8baf45f9c51614</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Co-op: Engineering, Data Analyst (Spring 2027)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Volvo Group</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Greensboro, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Power BI, Matplotlib, Seaborn, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a94aaab0838c666e</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=030b0793639a952d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a39ecc4ca815593a</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer III (Python/AWS)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9cadb9d904c7a2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer II</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>DAT Solutions</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=927113c8494fece3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Snowflake, Databricks, PySpark, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7b17b10d5bed91</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Prototyping &amp; Transformation Associate</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3631153498e82a69</t>
+          <t>https://www.indeed.com/viewjob?jk=b7fa6836e8c25f23</t>
         </is>
       </c>
     </row>
